--- a/data/trans_orig/IP74A5_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP74A5_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adulto según si ha resuelto los impuestos.. en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Adultos según si tienen resuelto el retraso en los pagos de los impuestos relacionados con vehículos, IBI, etc en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -848,7 +848,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>1311</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,07%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>969</t>
+          <t>902</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5123</t>
+          <t>4669</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>91,15%</t>
         </is>
       </c>
     </row>
@@ -1872,54 +1872,54 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2845</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>71,34%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>1,32%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2845</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>71,34%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>460</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4154</t>
+          <t>4223</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,09%</t>
+          <t>82,43%</t>
         </is>
       </c>
     </row>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3572</t>
+          <t>2860</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2122,44 +2122,44 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
+          <t>80,07%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>2296</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>832</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>2975</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>77,16%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>27,97%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>2296</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>832</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>2975</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>77,16%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>27,97%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>6</t>
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1461</t>
+          <t>1162</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5663</t>
+          <t>5565</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>86,49%</t>
+          <t>85,01%</t>
         </is>
       </c>
     </row>
@@ -2215,62 +2215,62 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
+          <t>731</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>3572</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>67,04%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>20,47%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>679</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>3572</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>67,04%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>2143</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>22,84%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>679</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>2597</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>22,84%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>72,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>982</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5087</t>
+          <t>5386</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,7%</t>
+          <t>82,27%</t>
         </is>
       </c>
     </row>
@@ -2515,7 +2515,7 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>671</t>
+          <t>663</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3545</t>
+          <t>3609</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,69%</t>
+          <t>85,2%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4560</t>
+          <t>4440</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10205</t>
+          <t>10088</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>36,68%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>83,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3178</t>
+          <t>3070</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7854</t>
+          <t>7713</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>36,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>9337</t>
+          <t>9271</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>16804</t>
+          <t>16900</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>45,6%</t>
+          <t>45,27%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>82,53%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>7545</t>
+          <t>7665</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>62,33%</t>
+          <t>63,32%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>515</t>
+          <t>660</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>5193</t>
+          <t>5307</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>62,03%</t>
+          <t>63,39%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3673</t>
+          <t>3577</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>11140</t>
+          <t>11206</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>54,4%</t>
+          <t>54,73%</t>
         </is>
       </c>
     </row>
